--- a/AAII_Financials/Quarterly/WKC_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/WKC_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="92">
   <si>
     <t>WKC</t>
   </si>
@@ -656,288 +656,301 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:V102"/>
+  <dimension ref="A5:W102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:23" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E7" s="2">
         <v>46112</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>46022</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45930</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45838</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45747</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45657</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45565</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45473</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45382</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45291</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45199</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45107</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>45016</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44926</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44834</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44742</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44651</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44561</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44469</v>
       </c>
     </row>
-    <row r="8" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>13591200</v>
+      </c>
+      <c r="E8" s="3">
         <v>9685000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>9029000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>9391800</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>9043300</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>9452500</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>9760500</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>10490900</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>10965200</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>10951400</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>12003000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>12245300</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>10980700</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>12481600</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>13877700</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>15661300</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>17122100</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>12382000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>9942800</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>8350900</v>
       </c>
     </row>
-    <row r="9" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>13226000</v>
+      </c>
+      <c r="E9" s="3">
         <v>9413800</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>8793600</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>9142200</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>8810900</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>9222100</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>9501600</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>10222800</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>10720000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>10697300</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>11721800</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>11963900</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>10699000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>12218900</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>13595400</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>15339000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>16868700</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>12151100</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>9727500</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>8153400</v>
       </c>
     </row>
-    <row r="10" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>365200</v>
+      </c>
+      <c r="E10" s="3">
         <v>271200</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>235400</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>249600</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>232400</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>230400</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>258900</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>268100</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>245200</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>254100</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>281200</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>281400</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>281700</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>262700</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>282300</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>322300</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>253400</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>230900</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>215300</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>197500</v>
       </c>
     </row>
-    <row r="11" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -960,8 +973,9 @@
       <c r="T11" s="3"/>
       <c r="U11" s="3"/>
       <c r="V11" s="3"/>
-    </row>
-    <row r="12" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W11" s="3"/>
+    </row>
+    <row r="12" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1022,8 +1036,11 @@
       <c r="V12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1084,115 +1101,121 @@
       <c r="V13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>6200</v>
+      </c>
+      <c r="E14" s="3">
         <v>6700</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>323700</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>4900</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>486300</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>59500</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>138000</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>1200</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>-88000</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>200</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>88500</v>
       </c>
-      <c r="N14" s="3" t="s">
+      <c r="O14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>300</v>
       </c>
-      <c r="P14" s="3" t="s">
+      <c r="Q14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>600</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>-800</v>
       </c>
-      <c r="S14" s="3">
-        <v>0</v>
-      </c>
       <c r="T14" s="3">
         <v>0</v>
       </c>
       <c r="U14" s="3">
+        <v>0</v>
+      </c>
+      <c r="V14" s="3">
         <v>-200</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>1700</v>
       </c>
     </row>
-    <row r="15" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>20200</v>
+      </c>
+      <c r="E15" s="3">
         <v>20000</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>4600</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>23500</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>23900</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>25600</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>7900</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>25500</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>24500</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>25300</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>1300</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>26100</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>25900</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>25800</v>
       </c>
-      <c r="Q15" s="3">
-        <v>0</v>
-      </c>
       <c r="R15" s="3">
         <v>0</v>
       </c>
@@ -1208,8 +1231,11 @@
       <c r="V15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:23" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1229,132 +1255,139 @@
       <c r="T16" s="3"/>
       <c r="U16" s="3"/>
       <c r="V16" s="3"/>
-    </row>
-    <row r="17" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W16" s="3"/>
+    </row>
+    <row r="17" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>13488800</v>
+      </c>
+      <c r="E17" s="3">
         <v>9622000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>8981300</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>9324100</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>8983700</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>9399600</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>9703800</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>10417500</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>10912000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>10887900</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>11929900</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>12172000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>10904900</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>12417100</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>13798900</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>15561000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>17069300</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>12340700</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>9910400</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>8309200</v>
       </c>
     </row>
-    <row r="18" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>102400</v>
+      </c>
+      <c r="E18" s="3">
         <v>63000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>47700</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>67700</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>59600</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>52900</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>56700</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>73400</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>53200</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>63500</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>73100</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>73300</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>75800</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>64500</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>78800</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>100300</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>52800</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>41300</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>32400</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>41700</v>
       </c>
     </row>
-    <row r="19" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1377,318 +1410,334 @@
       <c r="T19" s="3"/>
       <c r="U19" s="3"/>
       <c r="V19" s="3"/>
-    </row>
-    <row r="20" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W19" s="3"/>
+    </row>
+    <row r="20" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-800</v>
+      </c>
+      <c r="E20" s="3">
         <v>5000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-600</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-1900</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-3600</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>6700</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-1900</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-1400</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-2900</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>14100</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-1100</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-1600</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>2800</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>15100</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-13400</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-2800</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-2700</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>8100</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>700</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>2700</v>
       </c>
     </row>
-    <row r="21" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>123400</v>
+      </c>
+      <c r="E21" s="3">
         <v>78000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>52900</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>93100</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>87100</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>71800</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>66500</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>100300</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>80600</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>74700</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>75500</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>101000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>98900</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>75200</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>93100</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>124100</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>76400</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>76600</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>53900</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>64100</v>
       </c>
     </row>
-    <row r="22" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>33200</v>
+      </c>
+      <c r="E22" s="3">
         <v>20500</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>28800</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>28400</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>28200</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>18500</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>27000</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>29000</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>29200</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>20700</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>33200</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>31600</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>34900</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>24200</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>38000</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>34700</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>27800</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>16800</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>12600</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>12100</v>
       </c>
     </row>
-    <row r="23" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>66400</v>
+      </c>
+      <c r="E23" s="3">
         <v>32100</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-301600</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>38800</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-448700</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-28100</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-101200</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>49600</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>116600</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>30500</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-46700</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>46300</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>40200</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>26800</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>27400</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>62800</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>22300</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>32600</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>20500</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>32300</v>
       </c>
     </row>
-    <row r="24" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>16600</v>
+      </c>
+      <c r="E24" s="3">
         <v>6600</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>-22100</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>10700</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>-109600</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>-6800</v>
       </c>
-      <c r="I24" s="3">
-        <v>0</v>
-      </c>
       <c r="J24" s="3">
+        <v>0</v>
+      </c>
+      <c r="K24" s="3">
         <v>14600</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>9700</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>3300</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>-11800</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>10800</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>9800</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>4200</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>6500</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>18900</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>-2500</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>6400</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>5000</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>10000</v>
       </c>
     </row>
-    <row r="25" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1749,132 +1798,141 @@
       <c r="V25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>49800</v>
+      </c>
+      <c r="E26" s="3">
         <v>25500</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-279500</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>28100</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-339100</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-21300</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-101200</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>35000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>106900</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>27200</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-34900</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>35500</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>30400</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>22600</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>20900</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>43900</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>24800</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>26200</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>15500</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>22300</v>
       </c>
     </row>
-    <row r="27" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>48400</v>
+      </c>
+      <c r="E27" s="3">
         <v>26200</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-279700</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>25700</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-339400</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-21100</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-101800</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>33500</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>108300</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>27400</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-34800</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>34900</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>29900</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>22800</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>20900</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>42500</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>24400</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>26300</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>15500</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>21700</v>
       </c>
     </row>
-    <row r="28" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1935,8 +1993,11 @@
       <c r="V28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1997,8 +2058,11 @@
       <c r="V29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2059,8 +2123,11 @@
       <c r="V30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2121,132 +2188,141 @@
       <c r="V31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>800</v>
+      </c>
+      <c r="E32" s="3">
         <v>-5000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>600</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>1900</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>3600</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-6700</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>1900</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>1400</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>2900</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-14100</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>1100</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>1600</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-2800</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-15100</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>13400</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>2800</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>2700</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-8100</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-700</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-2700</v>
       </c>
     </row>
-    <row r="33" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>48400</v>
+      </c>
+      <c r="E33" s="3">
         <v>26200</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-279700</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>25700</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-339400</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-21100</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-101800</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>33500</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>108300</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>27400</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-34800</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>34900</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>29900</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>22800</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>20900</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>42500</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>24400</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>26300</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>15500</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>21700</v>
       </c>
     </row>
-    <row r="34" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2307,137 +2383,146 @@
       <c r="V34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>48400</v>
+      </c>
+      <c r="E35" s="3">
         <v>26200</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-279700</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>25700</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-339400</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-21100</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-101800</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>33500</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>108300</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>27400</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-34800</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>34900</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>29900</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>22800</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>20900</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>42500</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>24400</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>26300</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>15500</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>21700</v>
       </c>
     </row>
-    <row r="37" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E38" s="2">
         <v>46112</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>46022</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45930</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45838</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45747</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45657</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45565</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45473</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45382</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45291</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45199</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45107</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>45016</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44926</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44834</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44742</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44651</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44561</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44469</v>
       </c>
     </row>
-    <row r="39" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2460,8 +2545,9 @@
       <c r="T39" s="3"/>
       <c r="U39" s="3"/>
       <c r="V39" s="3"/>
-    </row>
-    <row r="40" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W39" s="3"/>
+    </row>
+    <row r="40" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2484,70 +2570,74 @@
       <c r="T40" s="3"/>
       <c r="U40" s="3"/>
       <c r="V40" s="3"/>
-    </row>
-    <row r="41" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W40" s="3"/>
+    </row>
+    <row r="41" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>135300</v>
+      </c>
+      <c r="E41" s="3">
         <v>151100</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>193500</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>473600</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>403200</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>456400</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>382900</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>373800</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>524600</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>321300</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>304300</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>335600</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>293900</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>216700</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>298400</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>280300</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>385800</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>266200</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>652200</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>796000</v>
       </c>
     </row>
-    <row r="42" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2567,26 +2657,26 @@
         <v>0</v>
       </c>
       <c r="I42" s="3">
+        <v>0</v>
+      </c>
+      <c r="J42" s="3">
         <v>2900</v>
       </c>
-      <c r="J42" s="3">
-        <v>0</v>
-      </c>
       <c r="K42" s="3">
+        <v>0</v>
+      </c>
+      <c r="L42" s="3">
         <v>10500</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>13400</v>
       </c>
-      <c r="M42" s="3">
-        <v>0</v>
-      </c>
       <c r="N42" s="3">
+        <v>0</v>
+      </c>
+      <c r="O42" s="3">
         <v>14500</v>
       </c>
-      <c r="O42" s="3">
-        <v>0</v>
-      </c>
       <c r="P42" s="3">
         <v>0</v>
       </c>
@@ -2608,256 +2698,271 @@
       <c r="V42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>2942200</v>
+      </c>
+      <c r="E43" s="3">
         <v>2843400</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>2208500</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>2078700</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>2143300</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>2245800</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>2432600</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>2476100</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>2592000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>2679000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>2735500</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>2882200</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>2473300</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>2997200</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>3294100</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>3172900</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>3954700</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>3510200</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>2355300</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>2032500</v>
       </c>
     </row>
-    <row r="44" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>579300</v>
+      </c>
+      <c r="E44" s="3">
         <v>739200</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>454200</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>501300</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>474900</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>503700</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>513500</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>619900</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>646700</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>654600</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>664600</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>654200</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>552600</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>618600</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>779900</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>727500</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>903800</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>680500</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>477900</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>439300</v>
       </c>
     </row>
-    <row r="45" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>482800</v>
+      </c>
+      <c r="E45" s="3">
         <v>556500</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>557700</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>504000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>473800</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>552800</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>555900</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>611100</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>538500</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>650400</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>721800</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>612300</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>640500</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>699900</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>865700</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>868600</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>649700</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>568400</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>534300</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>425400</v>
       </c>
     </row>
-    <row r="46" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>4216000</v>
+      </c>
+      <c r="E46" s="3">
         <v>4390700</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>3500500</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>3637500</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>3570900</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>3829900</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>3959200</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>4170700</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>4395600</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>4392600</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>4503800</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>4591300</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>4045100</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>4613800</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>5238100</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>5049300</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>5894000</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>5025300</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>4019700</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>3693200</v>
       </c>
     </row>
-    <row r="47" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2891,18 +2996,18 @@
       <c r="M47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="N47" s="3">
+      <c r="N47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O47" s="3">
         <v>6000</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>8300</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>8400</v>
       </c>
-      <c r="Q47" s="3">
-        <v>0</v>
-      </c>
       <c r="R47" s="3">
         <v>0</v>
       </c>
@@ -2918,132 +3023,141 @@
       <c r="V47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>349400</v>
+      </c>
+      <c r="E48" s="3">
         <v>347400</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>425600</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>448000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>451300</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>480100</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>596700</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>505600</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>495300</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>496100</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>581600</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>509800</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>507300</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>497000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>484200</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>475300</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>476000</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>473900</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>348900</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>334300</v>
       </c>
     </row>
-    <row r="49" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>1036400</v>
+      </c>
+      <c r="E49" s="3">
         <v>1044600</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>1128200</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>1064400</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>1073600</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>1434800</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>1532000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>1448000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>1450700</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>1459200</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>1651900</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>1540400</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>1554700</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>1561300</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>1569200</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>1566100</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>1590000</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>1614100</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>1573800</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>1516800</v>
       </c>
     </row>
-    <row r="50" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3104,8 +3218,11 @@
       <c r="V50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3166,70 +3283,76 @@
       <c r="V51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>997100</v>
+      </c>
+      <c r="E52" s="3">
         <v>1020300</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>595400</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>910500</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>958200</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>844300</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>565100</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>860300</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>847600</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>826500</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>554600</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>835600</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>846500</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>805300</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>873100</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>879600</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>835700</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>854700</v>
-      </c>
-      <c r="U52" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="V52" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="53" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W52" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="53" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3290,70 +3413,76 @@
       <c r="V53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>6598900</v>
+      </c>
+      <c r="E54" s="3">
         <v>6803000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>5863900</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>6060400</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>6054000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>6589100</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>6731800</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>6984600</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>7189200</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>7174400</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>7375300</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>7483100</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>6961900</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>7485800</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>8164600</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>7970300</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>8795700</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>7968000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>5942400</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>5544300</v>
       </c>
     </row>
-    <row r="55" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3376,8 +3505,9 @@
       <c r="T55" s="3"/>
       <c r="U55" s="3"/>
       <c r="V55" s="3"/>
-    </row>
-    <row r="56" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W55" s="3"/>
+    </row>
+    <row r="56" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3400,380 +3530,399 @@
       <c r="T56" s="3"/>
       <c r="U56" s="3"/>
       <c r="V56" s="3"/>
-    </row>
-    <row r="57" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W56" s="3"/>
+    </row>
+    <row r="57" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>3252100</v>
+      </c>
+      <c r="E57" s="3">
         <v>3413100</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>2586900</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>2523400</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>2536400</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>2529700</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>2726500</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>2750800</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>2975900</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>2965500</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>3097600</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>3293300</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>2708700</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>3213200</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>3529500</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>3237900</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>3936700</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>3447500</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>2399600</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>2024300</v>
       </c>
     </row>
-    <row r="58" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>8700</v>
+      </c>
+      <c r="E58" s="3">
         <v>9100</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>40100</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>28800</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>43200</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>86800</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>116100</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>85000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>81400</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>81100</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>111000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>63000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>61600</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>18200</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>15800</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>15700</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>16300</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>15000</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>30600</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>30100</v>
       </c>
     </row>
-    <row r="59" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>64400</v>
+      </c>
+      <c r="E59" s="3">
         <v>75200</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>52700</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>61700</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>73800</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>108800</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>91500</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>90300</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>101200</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>134900</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>128300</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>150400</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>212000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>252900</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>1063300</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>1314700</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>1141700</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>950000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>666500</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>642100</v>
       </c>
     </row>
-    <row r="60" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>3985200</v>
+      </c>
+      <c r="E60" s="3">
         <v>4200800</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>3310400</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>3153400</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>3149000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>3342300</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>3437800</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>3583100</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>3818900</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>3862400</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>4049700</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>4114200</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>3572000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>4153500</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>4608600</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>4568300</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>5094700</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>4412500</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>3096700</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>2696500</v>
       </c>
     </row>
-    <row r="61" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>736600</v>
+      </c>
+      <c r="E61" s="3">
         <v>789600</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>817900</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>766600</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>775200</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>792300</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>940900</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>798000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>797800</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>802600</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>967000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>812300</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>816200</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>708400</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>829900</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>693600</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>1024100</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>869100</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>478100</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>484200</v>
       </c>
     </row>
-    <row r="62" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>610000</v>
+      </c>
+      <c r="E62" s="3">
         <v>600800</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>413900</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>513900</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>525000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>526300</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>351600</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>552500</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>535100</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>550900</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>349700</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>581600</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>608400</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>609900</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>735400</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>762800</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>756700</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>740900</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>450800</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>439800</v>
       </c>
     </row>
-    <row r="63" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3834,8 +3983,11 @@
       <c r="V63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3896,8 +4048,11 @@
       <c r="V64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3958,70 +4113,76 @@
       <c r="V65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>5331800</v>
+      </c>
+      <c r="E66" s="3">
         <v>5591200</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>4556000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>4433900</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>4449200</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>4660900</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>4775900</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>4933600</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>5151800</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>5215900</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>5425600</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>5508100</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>4996600</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>5471800</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>6179800</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>6030600</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>6880000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>6026600</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>4029700</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>3624600</v>
       </c>
     </row>
-    <row r="67" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4044,8 +4205,9 @@
       <c r="T67" s="3"/>
       <c r="U67" s="3"/>
       <c r="V67" s="3"/>
-    </row>
-    <row r="68" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W67" s="3"/>
+    </row>
+    <row r="68" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4106,8 +4268,11 @@
       <c r="V68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4168,8 +4333,11 @@
       <c r="V69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4230,8 +4398,11 @@
       <c r="V70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4292,70 +4463,76 @@
       <c r="V71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>1289800</v>
+      </c>
+      <c r="E72" s="3">
         <v>1262700</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>1315900</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>1630600</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>1615900</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>1978500</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>2009200</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>2120600</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>2097000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>1998800</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>1981600</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>2024800</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>1998200</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>1976700</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>1962500</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>1950200</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>1916400</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>1899400</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>1880600</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>1872600</v>
       </c>
     </row>
-    <row r="73" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4416,8 +4593,11 @@
       <c r="V73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4478,8 +4658,11 @@
       <c r="V74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4540,70 +4723,76 @@
       <c r="V75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>1257600</v>
+      </c>
+      <c r="E76" s="3">
         <v>1203700</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>1299100</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>1617900</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>1598600</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>1921200</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>1948700</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>2044400</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>2032300</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>1952000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>1943000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>1968300</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>1959100</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>2008300</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>1984800</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>1939700</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>1915700</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>1941400</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>1912700</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>1919700</v>
       </c>
     </row>
-    <row r="77" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4664,137 +4853,146 @@
       <c r="V77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E80" s="2">
         <v>46112</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>46022</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45930</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45838</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45747</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45657</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45565</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45473</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45382</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45291</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45199</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45107</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>45016</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44926</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44834</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44742</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44651</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44561</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44469</v>
       </c>
     </row>
-    <row r="81" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>48400</v>
+      </c>
+      <c r="E81" s="3">
         <v>26200</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-279700</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>25700</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-339400</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-21100</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-101800</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>33500</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>108300</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>27400</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-34800</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>34900</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>29900</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>22800</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>20900</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>42500</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>24400</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>26300</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>15500</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>21700</v>
       </c>
     </row>
-    <row r="82" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4817,70 +5015,74 @@
       <c r="T82" s="3"/>
       <c r="U82" s="3"/>
       <c r="V82" s="3"/>
-    </row>
-    <row r="83" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W82" s="3"/>
+    </row>
+    <row r="83" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>23900</v>
+      </c>
+      <c r="E83" s="3">
         <v>25600</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>7900</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>25500</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>24500</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>25300</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>1300</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>26100</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>25900</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>25800</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>6700</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>26600</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>26300</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>27200</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>27700</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>26600</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>26300</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>27200</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>20800</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>19700</v>
       </c>
     </row>
-    <row r="84" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4941,8 +5143,11 @@
       <c r="V84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5003,8 +5208,11 @@
       <c r="V85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5065,8 +5273,11 @@
       <c r="V86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5127,8 +5338,11 @@
       <c r="V87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5189,70 +5403,76 @@
       <c r="V88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-21300</v>
+      </c>
+      <c r="E89" s="3">
         <v>-46400</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>34200</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>116100</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>28200</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>114400</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>120300</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-38500</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>67900</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>110200</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>4500</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>80300</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>43500</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>143000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-90800</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>258500</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>42900</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-72100</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-50200</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>82600</v>
       </c>
     </row>
-    <row r="90" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5275,8 +5495,9 @@
       <c r="T90" s="3"/>
       <c r="U90" s="3"/>
       <c r="V90" s="3"/>
-    </row>
-    <row r="91" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W90" s="3"/>
+    </row>
+    <row r="91" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -5284,61 +5505,64 @@
         <v>-13800</v>
       </c>
       <c r="E91" s="3">
+        <v>-13800</v>
+      </c>
+      <c r="F91" s="3">
         <v>-21400</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-14100</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-14900</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-15200</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-17900</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-18200</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-14600</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-17500</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-19700</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-21400</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-27700</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-18800</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-22400</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-18500</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-21000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-16700</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-10900</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-14100</v>
       </c>
     </row>
-    <row r="92" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5399,8 +5623,11 @@
       <c r="V92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5461,70 +5688,76 @@
       <c r="V93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>76300</v>
+      </c>
+      <c r="E94" s="3">
         <v>-11600</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-165200</v>
       </c>
-      <c r="F94" s="3">
-        <v>0</v>
-      </c>
       <c r="G94" s="3">
+        <v>0</v>
+      </c>
+      <c r="H94" s="3">
         <v>1000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-5800</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-34400</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-64900</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>180700</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-16900</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-23700</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-21300</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-32600</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-23500</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-25700</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-20700</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-21200</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-657300</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-48500</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>9900</v>
       </c>
     </row>
-    <row r="95" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5547,70 +5780,74 @@
       <c r="T95" s="3"/>
       <c r="U95" s="3"/>
       <c r="V95" s="3"/>
-    </row>
-    <row r="96" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W95" s="3"/>
+    </row>
+    <row r="96" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>10200</v>
+      </c>
+      <c r="E96" s="3">
         <v>10700</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>11000</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>11100</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>9500</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>9700</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>9900</v>
-      </c>
-      <c r="J96" s="3">
-        <v>10100</v>
       </c>
       <c r="K96" s="3">
         <v>10100</v>
       </c>
       <c r="L96" s="3">
+        <v>10100</v>
+      </c>
+      <c r="M96" s="3">
         <v>8400</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>8300</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>8400</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>8700</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>8600</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-8600</v>
       </c>
-      <c r="R96" s="3">
+      <c r="S96" s="3">
         <v>-7400</v>
       </c>
-      <c r="S96" s="3">
+      <c r="T96" s="3">
         <v>-7600</v>
       </c>
-      <c r="T96" s="3">
+      <c r="U96" s="3">
         <v>-7400</v>
       </c>
-      <c r="U96" s="3">
+      <c r="V96" s="3">
         <v>-7500</v>
       </c>
-      <c r="V96" s="3">
+      <c r="W96" s="3">
         <v>-7600</v>
       </c>
     </row>
-    <row r="97" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5671,8 +5908,11 @@
       <c r="V97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5733,8 +5973,11 @@
       <c r="V98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -5795,190 +6038,202 @@
       <c r="V99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-72900</v>
+      </c>
+      <c r="E100" s="3">
         <v>15400</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-151400</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-32600</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-98700</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-32400</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-68000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-47900</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-50400</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-64300</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-12000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-11100</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>63500</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-192800</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>122300</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-336000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>107300</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>343700</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-43300</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-34600</v>
       </c>
     </row>
-    <row r="101" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>16300</v>
+      </c>
+      <c r="E101" s="3">
         <v>-2700</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-8800</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>600</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-1200</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-5800</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-200</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-6200</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>2700</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-8300</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>12300</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-7300</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-9400</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-300</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>12300</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-7300</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>-9400</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>-300</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>-1800</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>-4600</v>
       </c>
     </row>
-    <row r="102" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-16100</v>
+      </c>
+      <c r="E102" s="3">
         <v>-42100</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-279500</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>70400</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-53200</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>73500</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>9100</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-150700</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>197000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>23200</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-31400</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>41700</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>77100</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-81600</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>18100</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-105500</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>119600</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-386000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-143800</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>53300</v>
       </c>
     </row>
